--- a/salidas/empresas/AMD.xlsx
+++ b/salidas/empresas/AMD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1318,7 +1330,7 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1337,7 +1349,7 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1356,7 +1368,7 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1375,7 +1387,7 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1394,7 +1406,7 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1413,7 +1425,7 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1432,7 +1444,7 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1451,7 +1463,7 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1470,7 +1482,7 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1489,7 +1501,7 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1508,7 +1520,7 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1527,7 +1539,7 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1552,7 +1564,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1577,7 +1589,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1602,7 +1614,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1627,7 +1639,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1652,7 +1664,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1677,7 +1689,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1702,7 +1714,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1727,7 +1739,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1752,7 +1764,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1777,7 +1789,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1802,7 +1814,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1827,7 +1839,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1852,7 +1864,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1877,7 +1889,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -1902,7 +1914,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -1927,7 +1939,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -1952,7 +1964,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -1977,7 +1989,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2006,7 +2018,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2035,7 +2047,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2064,7 +2076,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2091,7 +2103,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2118,7 +2130,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2145,7 +2157,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2172,7 +2184,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2199,7 +2211,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2226,7 +2238,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2253,7 +2265,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2280,7 +2292,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2307,7 +2319,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2334,7 +2346,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2361,7 +2373,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2388,7 +2400,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2415,7 +2427,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2442,7 +2454,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2469,7 +2481,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2496,7 +2508,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2523,7 +2535,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2550,7 +2562,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2577,7 +2589,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2604,7 +2616,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2631,7 +2643,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2658,7 +2670,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2685,7 +2697,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2712,7 +2724,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2741,7 +2753,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2770,7 +2782,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2799,7 +2811,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2828,7 +2840,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -2857,7 +2869,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -2886,7 +2898,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -2915,7 +2927,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -2944,7 +2956,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -2973,7 +2985,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3000,7 +3012,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3027,7 +3039,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3054,7 +3066,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3081,7 +3093,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3108,7 +3120,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3135,7 +3147,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3162,7 +3174,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3189,7 +3201,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3216,7 +3228,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3243,7 +3255,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3270,7 +3282,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3297,7 +3309,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3324,7 +3336,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3351,7 +3363,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3378,7 +3390,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3405,7 +3417,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3432,7 +3444,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3459,7 +3471,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3486,7 +3498,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3513,7 +3525,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3540,7 +3552,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3567,7 +3579,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3594,7 +3606,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3621,7 +3633,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3648,7 +3660,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3675,7 +3687,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3702,7 +3714,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3729,7 +3741,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3756,7 +3768,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3783,7 +3795,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -3810,7 +3822,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -3837,7 +3849,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -3864,7 +3876,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -3891,7 +3903,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -3918,7 +3930,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -3945,7 +3957,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -3974,7 +3986,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4003,7 +4015,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4032,7 +4044,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4061,7 +4073,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4090,7 +4102,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4119,7 +4131,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4148,7 +4160,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4177,7 +4189,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4206,7 +4218,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4235,7 +4247,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4264,7 +4276,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4293,7 +4305,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4322,7 +4334,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4351,7 +4363,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4380,7 +4392,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4409,7 +4421,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4438,7 +4450,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4467,7 +4479,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4496,7 +4508,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4525,7 +4537,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4554,7 +4566,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4583,7 +4595,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4612,7 +4624,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4641,7 +4653,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4670,7 +4682,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4699,7 +4711,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4728,7 +4740,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4757,7 +4769,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -4786,7 +4798,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -4815,7 +4827,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -4844,7 +4856,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -4873,7 +4885,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -4902,7 +4914,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -4931,7 +4943,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -4960,7 +4972,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -4989,7 +5001,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5018,7 +5030,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5047,7 +5059,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5076,7 +5088,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5105,7 +5117,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5134,7 +5146,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5163,7 +5175,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5192,7 +5204,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5221,7 +5233,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5250,7 +5262,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5279,7 +5291,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5308,7 +5320,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5337,7 +5349,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5366,7 +5378,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5395,7 +5407,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5424,7 +5436,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5453,7 +5465,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5482,7 +5494,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5511,7 +5523,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5540,7 +5552,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5569,7 +5581,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5598,7 +5610,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5627,7 +5639,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5656,7 +5668,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5685,7 +5697,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5714,7 +5726,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5743,7 +5755,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5772,7 +5784,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5801,7 +5813,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -5830,7 +5842,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -5859,7 +5871,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -5886,7 +5898,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -5913,7 +5925,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -5940,7 +5952,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -5969,7 +5981,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -5998,7 +6010,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6027,7 +6039,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6056,7 +6068,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6085,7 +6097,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6114,7 +6126,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6143,7 +6155,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6172,7 +6184,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6201,7 +6213,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6230,7 +6242,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6259,7 +6271,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6288,7 +6300,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6317,7 +6329,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6346,7 +6358,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6375,7 +6387,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6404,7 +6416,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6433,7 +6445,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6462,7 +6474,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6491,7 +6503,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6520,7 +6532,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6549,7 +6561,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6578,7 +6590,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6607,7 +6619,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6636,7 +6648,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6665,7 +6677,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6694,7 +6706,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6723,7 +6735,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6752,7 +6764,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6781,7 +6793,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6810,7 +6822,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6839,7 +6851,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6868,7 +6880,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -6897,7 +6909,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -6926,32 +6938,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>614.6099853515625</v>
+        <v>629.260009765625</v>
       </c>
       <c r="C250" t="n">
-        <v>614.6099853515625</v>
+        <v>629.260009765625</v>
       </c>
       <c r="D250" t="n">
-        <v>361719100</v>
+        <v>387017400</v>
       </c>
       <c r="E250" t="n">
         <v>3.89</v>
       </c>
       <c r="F250" t="n">
-        <v>157.9974255402474</v>
+        <v>161.7634986544023</v>
       </c>
       <c r="G250" t="n">
         <v>1632475042</v>
       </c>
       <c r="H250" t="n">
-        <v>1003335461650.411</v>
+        <v>1027251260871.059</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2215771088033577</v>
+        <v>0.2370740072851907</v>
       </c>
     </row>
   </sheetData>
@@ -6983,75 +6995,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39901</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39991</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7087,13 +7099,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39992</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40082</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7129,13 +7141,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40174</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40264</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7171,13 +7183,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40265</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40355</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7213,13 +7225,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40356</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40446</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7255,13 +7267,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40447</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40537</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7288,7 +7300,7 @@
       <c r="I7" t="n">
         <v>0.62</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K7" t="n">
@@ -7301,13 +7313,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40538</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40635</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7334,7 +7346,7 @@
       <c r="I8" t="n">
         <v>0.9500000000000001</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K8" t="n">
@@ -7347,13 +7359,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40636</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40726</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40765</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7380,7 +7392,7 @@
       <c r="I9" t="n">
         <v>1.09</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K9" t="n">
@@ -7393,13 +7405,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40727</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7426,7 +7438,7 @@
       <c r="I10" t="n">
         <v>1.39</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K10" t="n">
@@ -7439,13 +7451,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40818</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7472,7 +7484,7 @@
       <c r="I11" t="n">
         <v>0.6500000000000001</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K11" t="n">
@@ -7485,13 +7497,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7518,7 +7530,7 @@
       <c r="I12" t="n">
         <v>-0.83</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="K12" t="n">
@@ -7531,13 +7543,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7564,7 +7576,7 @@
       <c r="I13" t="n">
         <v>-0.8599999999999999</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="K13" t="n">
@@ -7577,13 +7589,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41181</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7610,7 +7622,7 @@
       <c r="I14" t="n">
         <v>-1.2</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="K14" t="n">
@@ -7623,13 +7635,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41272</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7656,7 +7668,7 @@
       <c r="I15" t="n">
         <v>-1.59</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="K15" t="n">
@@ -7669,13 +7681,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41273</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41363</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41400</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7702,7 +7714,7 @@
       <c r="I16" t="n">
         <v>-0.98</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41400</v>
       </c>
       <c r="K16" t="n">
@@ -7715,13 +7727,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41454</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7748,7 +7760,7 @@
       <c r="I17" t="n">
         <v>-1.13</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="K17" t="n">
@@ -7761,13 +7773,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41545</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7794,7 +7806,7 @@
       <c r="I18" t="n">
         <v>-0.8600000000000001</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="K18" t="n">
@@ -7807,13 +7819,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41546</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41636</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41688</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7840,7 +7852,7 @@
       <c r="I19" t="n">
         <v>-0.11</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41688</v>
       </c>
       <c r="K19" t="n">
@@ -7853,13 +7865,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41637</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41727</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7886,7 +7898,7 @@
       <c r="I20" t="n">
         <v>0.04999999999999999</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="K20" t="n">
@@ -7899,13 +7911,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41728</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41818</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -7932,7 +7944,7 @@
       <c r="I21" t="n">
         <v>0.09999999999999999</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K21" t="n">
@@ -7945,13 +7957,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41819</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41909</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -7978,7 +7990,7 @@
       <c r="I22" t="n">
         <v>0.06</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="K22" t="n">
@@ -7991,13 +8003,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41910</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42000</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8024,7 +8036,7 @@
       <c r="I23" t="n">
         <v>-0.53</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="K23" t="n">
@@ -8037,13 +8049,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42001</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42091</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8070,7 +8082,7 @@
       <c r="I24" t="n">
         <v>-0.73</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="K24" t="n">
@@ -8083,13 +8095,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42092</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42182</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8116,7 +8128,7 @@
       <c r="I25" t="n">
         <v>-0.91</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="K25" t="n">
@@ -8129,13 +8141,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42183</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42273</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8162,7 +8174,7 @@
       <c r="I26" t="n">
         <v>-1.18</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="K26" t="n">
@@ -8175,13 +8187,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42274</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42364</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8208,7 +8220,7 @@
       <c r="I27" t="n">
         <v>-0.84</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="K27" t="n">
@@ -8221,13 +8233,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42365</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42455</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8254,7 +8266,7 @@
       <c r="I28" t="n">
         <v>-0.75</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="K28" t="n">
@@ -8267,13 +8279,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42456</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42546</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8300,7 +8312,7 @@
       <c r="I29" t="n">
         <v>-0.44</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="K29" t="n">
@@ -8313,13 +8325,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42547</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42637</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8346,7 +8358,7 @@
       <c r="I30" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="K30" t="n">
@@ -8359,13 +8371,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42638</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8392,7 +8404,7 @@
       <c r="I31" t="n">
         <v>-0.62</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="K31" t="n">
@@ -8405,13 +8417,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8438,7 +8450,7 @@
       <c r="I32" t="n">
         <v>-0.5599999999999999</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="K32" t="n">
@@ -8451,13 +8463,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42827</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8484,7 +8496,7 @@
       <c r="I33" t="n">
         <v>-0.6599999999999999</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K33" t="n">
@@ -8497,13 +8509,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42918</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8530,7 +8542,7 @@
       <c r="I34" t="n">
         <v>-0.09</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K34" t="n">
@@ -8543,13 +8555,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43099</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8576,7 +8588,7 @@
       <c r="I35" t="n">
         <v>0.03</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="K35" t="n">
@@ -8589,13 +8601,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8622,7 +8634,7 @@
       <c r="I36" t="n">
         <v>0.19</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K36" t="n">
@@ -8635,13 +8647,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8668,7 +8680,7 @@
       <c r="I37" t="n">
         <v>0.32</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K37" t="n">
@@ -8681,13 +8693,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43372</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8714,7 +8726,7 @@
       <c r="I38" t="n">
         <v>0.34</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="K38" t="n">
@@ -8727,13 +8739,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43463</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8760,7 +8772,7 @@
       <c r="I39" t="n">
         <v>0.32</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="K39" t="n">
@@ -8773,13 +8785,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43464</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43554</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8806,7 +8818,7 @@
       <c r="I40" t="n">
         <v>0.25</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="K40" t="n">
@@ -8819,13 +8831,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43645</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8852,7 +8864,7 @@
       <c r="I41" t="n">
         <v>0.17</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="K41" t="n">
@@ -8865,13 +8877,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43736</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8898,7 +8910,7 @@
       <c r="I42" t="n">
         <v>0.19</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="K42" t="n">
@@ -8911,13 +8923,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43737</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43827</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -8944,7 +8956,7 @@
       <c r="I43" t="n">
         <v>0.3</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="K43" t="n">
@@ -8957,13 +8969,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43828</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43918</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -8990,7 +9002,7 @@
       <c r="I44" t="n">
         <v>0.43</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="K44" t="n">
@@ -9003,13 +9015,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43919</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44009</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9036,7 +9048,7 @@
       <c r="I45" t="n">
         <v>0.53</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K45" t="n">
@@ -9049,13 +9061,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44010</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44100</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9082,7 +9094,7 @@
       <c r="I46" t="n">
         <v>0.74</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="K46" t="n">
@@ -9095,13 +9107,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44101</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44191</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9128,7 +9140,7 @@
       <c r="I47" t="n">
         <v>2.04</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="K47" t="n">
@@ -9141,13 +9153,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44192</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44282</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9174,7 +9186,7 @@
       <c r="I48" t="n">
         <v>2.35</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="K48" t="n">
@@ -9187,13 +9199,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44283</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44373</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9220,7 +9232,7 @@
       <c r="I49" t="n">
         <v>2.8</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="K49" t="n">
@@ -9233,13 +9245,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44374</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44464</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9266,7 +9278,7 @@
       <c r="I50" t="n">
         <v>3.23</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="K50" t="n">
@@ -9279,13 +9291,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44465</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44555</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9312,7 +9324,7 @@
       <c r="I51" t="n">
         <v>2.569999999999999</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="K51" t="n">
@@ -9325,13 +9337,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44556</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44646</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9358,7 +9370,7 @@
       <c r="I52" t="n">
         <v>2.68</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K52" t="n">
@@ -9371,13 +9383,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44647</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44737</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9404,7 +9416,7 @@
       <c r="I53" t="n">
         <v>2.369999999999999</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K53" t="n">
@@ -9417,13 +9429,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44738</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44828</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9450,7 +9462,7 @@
       <c r="I54" t="n">
         <v>1.66</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K54" t="n">
@@ -9463,13 +9475,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44829</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9496,7 +9508,7 @@
       <c r="I55" t="n">
         <v>0.8399999999999997</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="K55" t="n">
@@ -9509,13 +9521,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9542,7 +9554,7 @@
       <c r="I56" t="n">
         <v>0.1899999999999997</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K56" t="n">
@@ -9555,13 +9567,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45018</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9588,7 +9600,7 @@
       <c r="I57" t="n">
         <v>-0.06000000000000034</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K57" t="n">
@@ -9601,13 +9613,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45109</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9634,7 +9646,7 @@
       <c r="I58" t="n">
         <v>0.07999999999999965</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="K58" t="n">
@@ -9647,13 +9659,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45290</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9680,7 +9692,7 @@
       <c r="I59" t="n">
         <v>0.5299999999999998</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="K59" t="n">
@@ -9693,13 +9705,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45381</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9726,7 +9738,7 @@
       <c r="I60" t="n">
         <v>0.6899999999999997</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K60" t="n">
@@ -9739,13 +9751,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45472</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9772,7 +9784,7 @@
       <c r="I61" t="n">
         <v>0.8299999999999997</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="K61" t="n">
@@ -9785,13 +9797,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45563</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9818,7 +9830,7 @@
       <c r="I62" t="n">
         <v>1.12</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K62" t="n">
@@ -9831,13 +9843,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45564</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45654</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9864,7 +9876,7 @@
       <c r="I63" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="K63" t="n">
@@ -9877,13 +9889,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45655</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45745</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -9910,7 +9922,7 @@
       <c r="I64" t="n">
         <v>1.37</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="K64" t="n">
@@ -9923,13 +9935,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45746</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45836</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -9956,7 +9968,7 @@
       <c r="I65" t="n">
         <v>1.75</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K65" t="n">
@@ -9969,13 +9981,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45837</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45927</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10002,7 +10014,7 @@
       <c r="I66" t="n">
         <v>2.03</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="K66" t="n">
@@ -10015,13 +10027,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46018</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10048,7 +10060,7 @@
       <c r="I67" t="n">
         <v>2.649999999999999</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="K67" t="n">
@@ -10061,13 +10073,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46019</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46109</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10094,7 +10106,7 @@
       <c r="I68" t="n">
         <v>3.05</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K68" t="n">
@@ -10107,13 +10119,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46110</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46200</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10140,7 +10152,7 @@
       <c r="I69" t="n">
         <v>3.89</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K69" t="n">
@@ -10177,52 +10189,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="C2" t="n">
@@ -10251,10 +10263,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40476</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="C3" t="n">
@@ -10283,10 +10295,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40588</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="C4" t="n">
@@ -10315,10 +10327,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40665</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="C5" t="n">
@@ -10347,10 +10359,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40757</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40765</v>
       </c>
       <c r="C6" t="n">
@@ -10379,10 +10391,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40848</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="C7" t="n">
@@ -10411,10 +10423,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40956</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C8" t="n">
@@ -10443,10 +10455,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41031</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="C9" t="n">
@@ -10475,10 +10487,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41211</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="C10" t="n">
@@ -10507,10 +10519,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41320</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="C11" t="n">
@@ -10539,10 +10551,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41393</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41400</v>
       </c>
       <c r="C12" t="n">
@@ -10571,10 +10583,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41484</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="C13" t="n">
@@ -10603,10 +10615,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41575</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="C14" t="n">
@@ -10635,10 +10647,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41688</v>
       </c>
       <c r="C15" t="n">
@@ -10667,10 +10679,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41757</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="C16" t="n">
@@ -10699,10 +10711,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41848</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C17" t="n">
@@ -10731,10 +10743,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41939</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="C18" t="n">
@@ -10763,10 +10775,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42048</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="C19" t="n">
@@ -10795,10 +10807,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42118</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="C20" t="n">
@@ -10827,10 +10839,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42209</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="C21" t="n">
@@ -10859,10 +10871,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42306</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="C22" t="n">
@@ -10891,10 +10903,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42412</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="C23" t="n">
@@ -10923,10 +10935,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42482</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="C24" t="n">
@@ -10955,10 +10967,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42572</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="C25" t="n">
@@ -10987,10 +10999,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42664</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="C26" t="n">
@@ -11019,10 +11031,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42776</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="C27" t="n">
@@ -11051,10 +11063,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42859</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="C28" t="n">
@@ -11083,10 +11095,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42944</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C29" t="n">
@@ -11115,10 +11127,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43035</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C30" t="n">
@@ -11147,10 +11159,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43154</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="C31" t="n">
@@ -11179,10 +11191,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43217</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C32" t="n">
@@ -11211,10 +11223,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43308</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C33" t="n">
@@ -11243,10 +11255,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43399</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="C34" t="n">
@@ -11275,10 +11287,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="C35" t="n">
@@ -11307,10 +11319,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43581</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C36" t="n">
@@ -11339,10 +11351,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43672</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C37" t="n">
@@ -11371,10 +11383,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43763</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="C38" t="n">
@@ -11403,10 +11415,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="C39" t="n">
@@ -11435,10 +11447,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43945</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C40" t="n">
@@ -11467,10 +11479,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44036</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C41" t="n">
@@ -11499,10 +11511,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44127</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="C42" t="n">
@@ -11531,10 +11543,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44218</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="C43" t="n">
@@ -11563,10 +11575,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44309</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="C44" t="n">
@@ -11595,10 +11607,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44400</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="C45" t="n">
@@ -11627,10 +11639,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44491</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="C46" t="n">
@@ -11659,10 +11671,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44589</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="C47" t="n">
@@ -11691,10 +11703,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44678</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C48" t="n">
@@ -11723,10 +11735,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44770</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C49" t="n">
@@ -11755,10 +11767,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44862</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C50" t="n">
@@ -11787,10 +11799,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44979</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="C51" t="n">
@@ -11819,10 +11831,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C52" t="n">
@@ -11851,10 +11863,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45135</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C53" t="n">
@@ -11883,10 +11895,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C54" t="n">
@@ -11915,10 +11927,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45316</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="C55" t="n">
@@ -11947,10 +11959,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45407</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C56" t="n">
@@ -11979,10 +11991,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45497</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="C57" t="n">
@@ -12011,10 +12023,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45588</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C58" t="n">
@@ -12043,10 +12055,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45687</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="C59" t="n">
@@ -12075,10 +12087,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45778</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C60" t="n">
@@ -12107,10 +12119,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45868</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C61" t="n">
@@ -12139,10 +12151,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45960</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="C62" t="n">
@@ -12171,10 +12183,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="C63" t="n">
@@ -12203,10 +12215,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46141</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C64" t="n">
@@ -12235,10 +12247,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46232</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C65" t="n">
@@ -12285,12 +12297,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
